--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484176_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484176_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4936</v>
+        <v>7.1683</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1136</v>
+        <v>6.6861</v>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>0.4822</v>
       </c>
       <c r="G2" t="n">
         <v>4.7147</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7366</v>
+        <v>1.4113</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0485</v>
+        <v>-0.476</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7851</v>
+        <v>1.8873</v>
       </c>
       <c r="V2" t="n">
         <v>2.431</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4459</v>
+        <v>3.7404</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1489</v>
+        <v>3.4153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.297</v>
+        <v>0.3251</v>
       </c>
       <c r="G3" t="n">
         <v>5.5638</v>
@@ -688,13 +688,13 @@
         <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6842</v>
+        <v>-0.3897</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9238</v>
+        <v>-0.6574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2396</v>
+        <v>0.2677</v>
       </c>
       <c r="V3" t="n">
         <v>0.7486</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1245</v>
+        <v>2.82</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8341</v>
+        <v>1.6742</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7096</v>
+        <v>1.1459</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8473</v>
+        <v>3.3407</v>
       </c>
       <c r="H4" t="n">
-        <v>1.996</v>
+        <v>2.4998</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8408</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0592</v>
+        <v>3.1705</v>
       </c>
       <c r="K4" t="n">
-        <v>2.778</v>
+        <v>2.4852</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2811</v>
+        <v>0.6853</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2119</v>
+        <v>0.1702</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.782</v>
+        <v>0.0147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5702</v>
+        <v>0.1555</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5952</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6675</v>
+        <v>0.999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6236</v>
+        <v>0.4875</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0439</v>
+        <v>0.5115</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7952</v>
+        <v>0.0675</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3417</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.1368</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9656</v>
+        <v>2.1258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9599</v>
+        <v>4.2843</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0056</v>
+        <v>-2.1585</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3407</v>
+        <v>2.8473</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4998</v>
+        <v>1.996</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8408</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1705</v>
+        <v>3.0592</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4852</v>
+        <v>2.778</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6853</v>
+        <v>0.2811</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1702</v>
+        <v>-0.2119</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0147</v>
+        <v>-0.782</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1555</v>
+        <v>0.5702</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5871</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1445</v>
+        <v>0.6688</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2267</v>
+        <v>0.0738</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3712</v>
+        <v>0.595</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0675</v>
+        <v>-0.7952</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.3417</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0675</v>
+        <v>-3.1368</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.342</v>
+        <v>1.7997</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9697</v>
+        <v>1.726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6277</v>
+        <v>0.0737</v>
       </c>
       <c r="G6" t="n">
         <v>2.8266</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2352</v>
+        <v>0.2225</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2722</v>
+        <v>0.0285</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5074</v>
+        <v>0.194</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4478</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5742</v>
+        <v>-0.49</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9862</v>
       </c>
       <c r="F7" t="n">
-        <v>0.412</v>
+        <v>0.4962</v>
       </c>
       <c r="G7" t="n">
         <v>0.8162</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.4435</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0611</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6767</v>
+        <v>-1.0863</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4359</v>
+        <v>-0.7614</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2407</v>
+        <v>-0.3249</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5644</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6967</v>
+        <v>-0.1063</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8501</v>
+        <v>-0.1756</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1535</v>
+        <v>0.0693</v>
       </c>
       <c r="V8" t="n">
         <v>1.9731</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8608</v>
+        <v>-1.5344</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9468</v>
+        <v>-0.8448</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.914</v>
+        <v>-0.6896</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4123</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5079</v>
+        <v>-0.1814</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2585</v>
+        <v>-0.034</v>
       </c>
       <c r="V9" t="n">
         <v>-1.139</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8424</v>
+        <v>-3.0313</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3153</v>
+        <v>-0.0092</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.527</v>
+        <v>-3.022</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2491</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0147</v>
+        <v>0.7964</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.2098</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0815</v>
+        <v>0.5865</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3882</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1005</v>
+        <v>-5.8834</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6475</v>
+        <v>-7.1779</v>
       </c>
       <c r="F11" t="n">
-        <v>1.547</v>
+        <v>1.2945</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6968</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2269</v>
+        <v>1.444</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2447</v>
+        <v>0.7143</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9822</v>
+        <v>0.7297</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4645</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.316999999999998</v>
+        <v>5.6288</v>
       </c>
       <c r="E12" t="n">
-        <v>7.694499999999999</v>
+        <v>8.006399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.377400000000001</v>
+        <v>-2.3774</v>
       </c>
       <c r="G12" t="n">
         <v>15.1867</v>
@@ -1390,13 +1390,13 @@
         <v>6.9434</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1091</v>
+        <v>4.4211</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5658999999999996</v>
+        <v>-0.2541999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>4.6751</v>
+        <v>4.6752</v>
       </c>
       <c r="V12" t="n">
         <v>-2.075599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0956</v>
+        <v>3.2044</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2022</v>
+        <v>2.59</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1066</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.6404</v>
@@ -1468,13 +1468,13 @@
         <v>2.579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6756</v>
+        <v>-0.5668</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1872</v>
+        <v>-0.425</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8627</v>
+        <v>-0.1418</v>
       </c>
       <c r="V13" t="n">
         <v>1.5437</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9668</v>
+        <v>0.9768</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6086</v>
+        <v>-1.0319</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6418</v>
+        <v>2.0087</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.8753</v>
+        <v>1.3868</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9109</v>
+        <v>-1.7483</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.9644</v>
+        <v>3.1352</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.8553</v>
+        <v>0.9348</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3354</v>
+        <v>-1.3647</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.52</v>
+        <v>2.2994</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.02</v>
+        <v>0.452</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5755</v>
+        <v>-0.3837</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4444</v>
+        <v>0.8357</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7774</v>
+        <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.1279</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0738</v>
+        <v>-0.9748</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4861</v>
+        <v>-0.1531</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4886</v>
+        <v>-0.8692</v>
       </c>
       <c r="W14" t="n">
-        <v>8.374000000000001</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.8854</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2268</v>
+        <v>0.472</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2714</v>
+        <v>3.0985</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4982</v>
+        <v>-2.6265</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1564</v>
+        <v>-4.8753</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2924</v>
+        <v>-0.9109</v>
       </c>
       <c r="I15" t="n">
-        <v>0.136</v>
+        <v>-3.9644</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0403</v>
+        <v>-2.8553</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0403</v>
+        <v>-0.3354</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1967</v>
+        <v>-2.02</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3328</v>
+        <v>-0.5755</v>
       </c>
       <c r="O15" t="n">
-        <v>0.136</v>
+        <v>-1.4444</v>
       </c>
       <c r="P15" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7935</v>
+        <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4104</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3117</v>
+        <v>-0.4363</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.4886</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.8854</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0206</v>
+        <v>0.2829</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2446</v>
+        <v>-0.2714</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2652</v>
+        <v>0.5543</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7804</v>
+        <v>-0.1564</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6002</v>
+        <v>-0.2924</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1802</v>
+        <v>0.136</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4688</v>
+        <v>0.0403</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2165</v>
+        <v>0.0403</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6853</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2492</v>
+        <v>-0.1967</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3837</v>
+        <v>-0.3328</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8655</v>
+        <v>0.136</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5776</v>
+        <v>-0.3542</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4307</v>
+        <v>-0.3117</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0082</v>
+        <v>-0.0425</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1421</v>
+        <v>0.2125</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5421</v>
+        <v>2.7301</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>-2.5175</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3868</v>
+        <v>1.1343</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7483</v>
+        <v>2.9481</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1352</v>
+        <v>-1.8138</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9348</v>
+        <v>4.164</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3647</v>
+        <v>3.5941</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2994</v>
+        <v>0.5699</v>
       </c>
       <c r="M17" t="n">
-        <v>0.452</v>
+        <v>-3.0297</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3837</v>
+        <v>-0.646</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8357</v>
+        <v>-2.3837</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>2.579</v>
+        <v>2.7774</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2468</v>
+        <v>-0.3656</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4849</v>
+        <v>-0.442</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7619</v>
+        <v>0.0764</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8692</v>
+        <v>-2.3417</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8692</v>
+        <v>-2.3417</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6904</v>
+        <v>-0.1575</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6281</v>
+        <v>1.4487</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3184</v>
+        <v>-1.6061</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1343</v>
+        <v>-1.7804</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9481</v>
+        <v>-0.6002</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8138</v>
+        <v>-1.1802</v>
       </c>
       <c r="J18" t="n">
-        <v>4.164</v>
+        <v>0.4688</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5941</v>
+        <v>-0.2165</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5699</v>
+        <v>0.6853</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0297</v>
+        <v>-2.2492</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.646</v>
+        <v>-0.3837</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3837</v>
+        <v>-1.8655</v>
       </c>
       <c r="P18" t="n">
         <v>1.7855</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7774</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2685</v>
+        <v>0.4407</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.544</v>
+        <v>-0.2266</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7245</v>
+        <v>0.6673</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3417</v>
+        <v>-0.6032</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3417</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3021</v>
+        <v>-1.0988</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1551</v>
+        <v>-0.747</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.147</v>
+        <v>-0.3518</v>
       </c>
       <c r="G19" t="n">
         <v>-5.3582</v>
@@ -1936,13 +1936,13 @@
         <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2545</v>
+        <v>0.4577</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8557</v>
+        <v>-0.4476</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1102</v>
+        <v>0.9054</v>
       </c>
       <c r="V19" t="n">
         <v>2.4129</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3479</v>
+        <v>-3.398</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2846</v>
+        <v>-3.3866</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0633</v>
+        <v>-0.0114</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8189</v>
@@ -2014,13 +2014,13 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4415</v>
+        <v>-0.4917</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5044</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1147</v>
       </c>
       <c r="V20" t="n">
         <v>-1.881</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1031</v>
+        <v>-3.7707</v>
       </c>
       <c r="E21" t="n">
         <v>-2.0528</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0503</v>
+        <v>-1.7179</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3588</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4585</v>
+        <v>-0.1261</v>
       </c>
       <c r="T21" t="n">
         <v>-0.8047</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3463</v>
+        <v>0.6787</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6745</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.317</v>
+        <v>-3.2764</v>
       </c>
       <c r="E22" t="n">
-        <v>2.377500000000001</v>
+        <v>2.377600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.6944</v>
+        <v>-5.653799999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-15.1865</v>
@@ -2143,7 +2143,7 @@
         <v>-12.7936</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7996999999999997</v>
+        <v>-0.7997000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>1.4684</v>
@@ -2170,13 +2170,13 @@
         <v>18.8466</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.1092</v>
+        <v>-2.0687</v>
       </c>
       <c r="T22" t="n">
         <v>-4.6751</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5658999999999998</v>
+        <v>2.6066</v>
       </c>
       <c r="V22" t="n">
         <v>2.075600000000001</v>
